--- a/media/exports/reports/2026-08/growth-services.xlsx
+++ b/media/exports/reports/2026-08/growth-services.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>August's client work made $68,020 gross margin (59.3%). Consultant time not charged to client work took $6,780 and overheads $53,650, leaving $7,590 profit before tax (6.6% of revenue). To cover overheads, client work needs a 52.7% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>August's client work made $79,880 gross margin (63.1%). Consultant time not charged to client work took $15,000 and overheads $53,650, leaving $11,230 profit before tax (8.9% of revenue). To cover overheads, client work needs a 54.3% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -860,10 +860,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="75" customHeight="1">
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Gross margin = revenue less contractors and consultant time charged to the work at $60 an hour (wages and all on-costs). Not included: consultant time not charged to clients, and overheads (management and admin wages, marketing, rent, IT, insurance, travel, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Gross margin is not profit. Gross margin = revenue less contractors and consultant time charged to the work at $60 an hour (wages and all on-costs). Not included: consultant time not charged to clients, and overheads (management and admin wages, marketing, rent, IT, insurance, travel, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>$114,640 against $61,475</t>
+          <t>$126,500 against $67,745</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>$235,395 against $147,795</t>
+          <t>$259,955 against $162,550</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>$141,095 before overheads</t>
+          <t>$165,655 before overheads</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Revenue is 59.3% up on the same period last year, year to date ($235,395 against $147,795). Training makes the highest gross margin (68.4%); Projects the lowest (58.9%). The business needs 52.7% gross margin just to cover overheads.</t>
+          <t>Revenue is 59.9% up on the same period last year, year to date ($259,955 against $162,550). Training makes the highest gross margin (71.3%); Projects the lowest (62.9%). The business needs 54.3% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Projects: 58.9% gross margin, 18.9 points over the 40.0% target ($29,357 ahead on $155,195 this financial year to date). Training: 68.4% gross margin, 28.4 points over the 40.0% target ($4,320 ahead on $15,200 this financial year to date).</t>
+          <t>Projects: 62.9% gross margin, 22.9 points over the 40.0% target ($39,353 ahead on $171,855 this financial year to date). Training: 71.3% gross margin, 31.3 points over the 40.0% target ($5,220 ahead on $16,700 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>$75,740 against $38,775</t>
+          <t>$83,800 against $42,845</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>$155,195 against $103,595</t>
+          <t>$171,855 against $114,050</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>$91,435 before overheads</t>
+          <t>$108,095 before overheads</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Projects brought in $155,195 this financial year to date, 49.8% on the same period last year (slower than the business as a whole, 59.3%), at a 58.9% gross margin (below the 59.9% overall).</t>
+          <t>Projects brought in $171,855 this financial year to date, 50.7% on the same period last year (slower than the business as a whole, 59.9%), at a 62.9% gross margin (below the 63.7% overall).</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Projects: 58.9% gross margin, 18.9 points over the 40.0% target ($29,357 ahead on $155,195 this financial year to date).</t>
+          <t>Projects: 62.9% gross margin, 22.9 points over the 40.0% target ($39,353 ahead on $171,855 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>$32,500 against $16,300</t>
+          <t>$35,700 against $17,900</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>$65,000 against $32,600</t>
+          <t>$71,400 against $35,800</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>$39,260 before overheads</t>
+          <t>$45,660 before overheads</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Retainers brought in $65,000 this financial year to date, 99.4% on the same period last year (faster than the business as a whole, 59.3%), at a 60.4% gross margin (above the 59.9% overall).</t>
+          <t>Retainers brought in $71,400 this financial year to date, 99.4% on the same period last year (faster than the business as a whole, 59.9%), at a 63.9% gross margin (above the 63.7% overall).</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Retainers: 60.4% gross margin, 20.4 points over the 40.0% target ($13,260 ahead on $65,000 this financial year to date).</t>
+          <t>Retainers: 63.9% gross margin, 23.9 points over the 40.0% target ($17,100 ahead on $71,400 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>$6,400 against $6,400</t>
+          <t>$7,000 against $7,000</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>$15,200 against $11,600</t>
+          <t>$16,700 against $12,700</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>$10,400 before overheads</t>
+          <t>$11,900 before overheads</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Training brought in $15,200 this financial year to date, 31.0% on the same period last year (slower than the business as a whole, 59.3%), at a 68.4% gross margin (above the 59.9% overall).</t>
+          <t>Training brought in $16,700 this financial year to date, 31.5% on the same period last year (slower than the business as a whole, 59.9%), at a 71.3% gross margin (above the 63.7% overall).</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Training: 68.4% gross margin, 28.4 points over the 40.0% target ($4,320 ahead on $15,200 this financial year to date).</t>
+          <t>Training: 71.3% gross margin, 31.3 points over the 40.0% target ($5,220 ahead on $16,700 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>68020</v>
+        <v>79880</v>
       </c>
     </row>
     <row r="9">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>46500</v>
+        <v>54720</v>
       </c>
     </row>
     <row r="10">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>114640</v>
+        <v>126500</v>
       </c>
     </row>
     <row r="16">
@@ -1506,7 +1506,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ties to the August 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the August 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>114640</v>
+        <v>126500</v>
       </c>
     </row>
     <row r="26">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>61475</v>
+        <v>67745</v>
       </c>
     </row>
     <row r="27">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>235395</v>
+        <v>259955</v>
       </c>
     </row>
     <row r="34">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>147795</v>
+        <v>162550</v>
       </c>
     </row>
     <row r="35">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>141095</v>
+        <v>165655</v>
       </c>
     </row>
     <row r="37">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>235395</v>
+        <v>259955</v>
       </c>
     </row>
     <row r="44">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>147795</v>
+        <v>162550</v>
       </c>
     </row>
     <row r="45">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>141095</v>
+        <v>165655</v>
       </c>
     </row>
     <row r="47">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>75740</v>
+        <v>83800</v>
       </c>
     </row>
     <row r="54">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>38775</v>
+        <v>42845</v>
       </c>
     </row>
     <row r="55">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>155195</v>
+        <v>171855</v>
       </c>
     </row>
     <row r="62">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>103595</v>
+        <v>114050</v>
       </c>
     </row>
     <row r="63">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>91435</v>
+        <v>108095</v>
       </c>
     </row>
     <row r="65">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>155195</v>
+        <v>171855</v>
       </c>
     </row>
     <row r="72">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>103595</v>
+        <v>114050</v>
       </c>
     </row>
     <row r="73">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>91435</v>
+        <v>108095</v>
       </c>
     </row>
     <row r="75">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="B81" s="12" t="n">
-        <v>32500</v>
+        <v>35700</v>
       </c>
     </row>
     <row r="82">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="B82" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="83">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="B89" s="12" t="n">
-        <v>65000</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="90">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="B90" s="12" t="n">
-        <v>32600</v>
+        <v>35800</v>
       </c>
     </row>
     <row r="91">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="B92" s="12" t="n">
-        <v>39260</v>
+        <v>45660</v>
       </c>
     </row>
     <row r="93">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="B99" s="12" t="n">
-        <v>65000</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="100">
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="B100" s="12" t="n">
-        <v>32600</v>
+        <v>35800</v>
       </c>
     </row>
     <row r="101">
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B102" s="12" t="n">
-        <v>39260</v>
+        <v>45660</v>
       </c>
     </row>
     <row r="103">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B109" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="110">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B110" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="111">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="B117" s="12" t="n">
-        <v>15200</v>
+        <v>16700</v>
       </c>
     </row>
     <row r="118">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="B118" s="12" t="n">
-        <v>11600</v>
+        <v>12700</v>
       </c>
     </row>
     <row r="119">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="B120" s="12" t="n">
-        <v>10400</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="121">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="B127" s="12" t="n">
-        <v>15200</v>
+        <v>16700</v>
       </c>
     </row>
     <row r="128">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="B128" s="12" t="n">
-        <v>11600</v>
+        <v>12700</v>
       </c>
     </row>
     <row r="129">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="B130" s="12" t="n">
-        <v>10400</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="131">
@@ -2347,7 +2347,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2397,7 +2397,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="D6" s="12" t="n">
-        <v>94520</v>
+        <v>103550</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>35320</v>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>108140</v>
+        <v>118390</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>40040</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>114895</v>
+        <v>125715</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>42940</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>88250</v>
+        <v>96560</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>33260</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>111010</v>
+        <v>121275</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>42820</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>77175</v>
+        <v>84340</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>31940</v>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>63970</v>
+        <v>69985</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>25520</v>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>95555</v>
+        <v>104970</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>36100</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>90220</v>
+        <v>99060</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>35380</v>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>86320</v>
+        <v>94805</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>32820</v>
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>61475</v>
+        <v>67745</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>21360</v>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>59535</v>
+        <v>65650</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>20280</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>71260</v>
+        <v>78550</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>25540</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>83940</v>
+        <v>92575</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>31140</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>69420</v>
+        <v>76600</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>24520</v>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>92370</v>
+        <v>102350</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>32520</v>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>100055</v>
+        <v>110835</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>36580</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>109865</v>
+        <v>121215</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>40720</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>80590</v>
+        <v>88665</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>27860</v>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>77090</v>
+        <v>84920</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>27680</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>115550</v>
+        <v>127580</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>46060</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>120755</v>
+        <v>133455</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>47680</v>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>114640</v>
+        <v>126500</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>46620</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>70720</v>
+        <v>77350</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>27820</v>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>88540</v>
+        <v>96790</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>34400</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>94695</v>
+        <v>103515</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>36880</v>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>66850</v>
+        <v>73060</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>26240</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>84410</v>
+        <v>92075</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>34360</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>48975</v>
+        <v>53340</v>
       </c>
       <c r="E34" s="12" t="n">
         <v>21860</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>37570</v>
+        <v>40885</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>17660</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>59755</v>
+        <v>65570</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>23980</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>64520</v>
+        <v>70760</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>26860</v>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>64820</v>
+        <v>71205</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>25920</v>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>38775</v>
+        <v>42845</v>
       </c>
       <c r="E39" s="12" t="n">
         <v>13860</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>38035</v>
+        <v>42050</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>13560</v>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>45860</v>
+        <v>50650</v>
       </c>
       <c r="E41" s="12" t="n">
         <v>18220</v>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>46840</v>
+        <v>51775</v>
       </c>
       <c r="E42" s="12" t="n">
         <v>18960</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>29520</v>
+        <v>32800</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>12340</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>60170</v>
+        <v>66950</v>
       </c>
       <c r="E44" s="12" t="n">
         <v>22440</v>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>62955</v>
+        <v>70035</v>
       </c>
       <c r="E45" s="12" t="n">
         <v>23440</v>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>75165</v>
+        <v>83115</v>
       </c>
       <c r="E46" s="12" t="n">
         <v>29380</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>47090</v>
+        <v>51865</v>
       </c>
       <c r="E47" s="12" t="n">
         <v>17480</v>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>43590</v>
+        <v>48120</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>16220</v>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>76650</v>
+        <v>84880</v>
       </c>
       <c r="E49" s="12" t="n">
         <v>31780</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="D50" s="12" t="n">
-        <v>79455</v>
+        <v>88055</v>
       </c>
       <c r="E50" s="12" t="n">
         <v>32080</v>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>75740</v>
+        <v>83800</v>
       </c>
       <c r="E51" s="12" t="n">
         <v>31680</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="D52" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E52" s="12" t="n">
         <v>4800</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E53" s="12" t="n">
         <v>4800</v>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="D54" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>5100</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E55" s="12" t="n">
         <v>4920</v>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="D56" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E56" s="12" t="n">
         <v>5400</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>21800</v>
+        <v>24000</v>
       </c>
       <c r="E57" s="12" t="n">
         <v>7980</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="D58" s="12" t="n">
-        <v>21800</v>
+        <v>24000</v>
       </c>
       <c r="E58" s="12" t="n">
         <v>7020</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>21800</v>
+        <v>24000</v>
       </c>
       <c r="E59" s="12" t="n">
         <v>8460</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="D60" s="12" t="n">
-        <v>21800</v>
+        <v>24000</v>
       </c>
       <c r="E60" s="12" t="n">
         <v>7800</v>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
       <c r="E61" s="12" t="n">
         <v>5940</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="D62" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
       <c r="E62" s="12" t="n">
         <v>5400</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>5760</v>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="D64" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>5640</v>
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>9480</v>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="D66" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E66" s="12" t="n">
         <v>9120</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E67" s="12" t="n">
         <v>9360</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="D68" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E68" s="12" t="n">
         <v>10440</v>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E69" s="12" t="n">
         <v>9240</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="D70" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E70" s="12" t="n">
         <v>9420</v>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E71" s="12" t="n">
         <v>10500</v>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="D72" s="12" t="n">
-        <v>32500</v>
+        <v>35700</v>
       </c>
       <c r="E72" s="12" t="n">
         <v>12180</v>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>32500</v>
+        <v>35700</v>
       </c>
       <c r="E73" s="12" t="n">
         <v>12900</v>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="D74" s="12" t="n">
-        <v>32500</v>
+        <v>35700</v>
       </c>
       <c r="E74" s="12" t="n">
         <v>12840</v>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="E75" s="12" t="n">
         <v>2700</v>
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="D76" s="12" t="n">
-        <v>4600</v>
+        <v>5100</v>
       </c>
       <c r="E76" s="12" t="n">
         <v>840</v>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E77" s="12" t="n">
         <v>960</v>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="D78" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E78" s="12" t="n">
         <v>2100</v>
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>11600</v>
+        <v>12700</v>
       </c>
       <c r="E79" s="12" t="n">
         <v>3060</v>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="D80" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E80" s="12" t="n">
         <v>2100</v>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="D81" s="12" t="n">
-        <v>4600</v>
+        <v>5100</v>
       </c>
       <c r="E81" s="12" t="n">
         <v>840</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="D82" s="12" t="n">
-        <v>14000</v>
+        <v>15400</v>
       </c>
       <c r="E82" s="12" t="n">
         <v>3660</v>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>3900</v>
+        <v>4300</v>
       </c>
       <c r="E83" s="12" t="n">
         <v>720</v>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="D84" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E84" s="12" t="n">
         <v>960</v>
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E85" s="12" t="n">
         <v>2100</v>
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="D86" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E86" s="12" t="n">
         <v>960</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>9100</v>
+        <v>10000</v>
       </c>
       <c r="E87" s="12" t="n">
         <v>1680</v>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="D88" s="12" t="n">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="E88" s="12" t="n">
         <v>2700</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>11600</v>
+        <v>12700</v>
       </c>
       <c r="E89" s="12" t="n">
         <v>3060</v>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="D90" s="12" t="n">
-        <v>3900</v>
+        <v>4300</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>720</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="E91" s="12" t="n">
         <v>2700</v>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="D92" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>2100</v>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>960</v>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="D94" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E94" s="12" t="n">
         <v>960</v>
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D95" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E95" s="12" t="n">
         <v>2100</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="D96" s="12" t="n">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>2700</v>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>2100</v>
@@ -5297,7 +5297,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5349,7 +5349,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -5393,17 +5393,17 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>155195</v>
+        <v>171855</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>103595</v>
+        <v>114050</v>
       </c>
       <c r="D6" s="13">
         <f>IF(C6=0,"",B6/C6-1)</f>
         <v/>
       </c>
       <c r="E6" s="12" t="n">
-        <v>91435</v>
+        <v>108095</v>
       </c>
       <c r="F6" s="13">
         <f>IF(B6=0,"",E6/B6)</f>
@@ -5417,17 +5417,17 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>65000</v>
+        <v>71400</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>32600</v>
+        <v>35800</v>
       </c>
       <c r="D7" s="13">
         <f>IF(C7=0,"",B7/C7-1)</f>
         <v/>
       </c>
       <c r="E7" s="12" t="n">
-        <v>39260</v>
+        <v>45660</v>
       </c>
       <c r="F7" s="13">
         <f>IF(B7=0,"",E7/B7)</f>
@@ -5441,17 +5441,17 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>15200</v>
+        <v>16700</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>11600</v>
+        <v>12700</v>
       </c>
       <c r="D8" s="13">
         <f>IF(C8=0,"",B8/C8-1)</f>
         <v/>
       </c>
       <c r="E8" s="12" t="n">
-        <v>10400</v>
+        <v>11900</v>
       </c>
       <c r="F8" s="13">
         <f>IF(B8=0,"",E8/B8)</f>
@@ -5465,17 +5465,17 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>235395</v>
+        <v>259955</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>147795</v>
+        <v>162550</v>
       </c>
       <c r="D9" s="13">
         <f>IF(C9=0,"",B9/C9-1)</f>
         <v/>
       </c>
       <c r="E9" s="12" t="n">
-        <v>141095</v>
+        <v>165655</v>
       </c>
       <c r="F9" s="13">
         <f>IF(B9=0,"",E9/B9)</f>
@@ -5488,7 +5488,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-08/growth-services.xlsx
+++ b/media/exports/reports/2026-08/growth-services.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>Workings!B37</f>
+        <f>Workings!B35</f>
         <v/>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B29" s="9">
-        <f>Workings!B65</f>
+        <f>Workings!B63</f>
         <v/>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B41" s="9">
-        <f>Workings!B93</f>
+        <f>Workings!B91</f>
         <v/>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B53" s="9">
-        <f>Workings!B121</f>
+        <f>Workings!B119</f>
         <v/>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2397,7 +2397,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5349,7 +5349,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: August 2026 · Data status: Jul 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
